--- a/apps/shell/resources/builtin-skills/cheil-media-plan/assets/미디어 플랜.xlsx
+++ b/apps/shell/resources/builtin-skills/cheil-media-plan/assets/미디어 플랜.xlsx
@@ -509,14 +509,21 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[광고주명] [캠페인명] 미디어 플랜</t>
+          <t>[광고주] [캠페인명] 미디어 플랜</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>작성 [날짜] · [팀명] · 숫자는 매체 견적·합의 자료 기준(출처는 '가정·출처' 시트)</t>
+          <t>작성 [작성일] · [팀명] · 캠페인 기간 [캠페인 기간] · 총예산 [총예산]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>숫자는 매체 견적·합의 자료 기준(출처는 '가정·출처' 시트)</t>
         </is>
       </c>
     </row>

--- a/apps/shell/resources/builtin-skills/cheil-media-plan/assets/미디어 플랜.xlsx
+++ b/apps/shell/resources/builtin-skills/cheil-media-plan/assets/미디어 플랜.xlsx
@@ -21,7 +21,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,11 +43,23 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="000B3D91"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001A1A1A"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
@@ -61,7 +73,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -70,16 +82,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00EEF2F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="000B3D91"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF2F8"/>
+        <fgColor rgb="00F4F5F7"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -101,29 +118,84 @@
         <color rgb="00D5D9E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D5D9E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D5D9E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D5D9E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D5D9E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D5D9E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D5D9E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D5D9E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D5D9E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -489,21 +561,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -516,394 +591,963 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>작성 [작성일] · [팀명] · 캠페인 기간 [캠페인 기간] · 총예산 [총예산]</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>숫자는 매체 견적·합의 자료 기준(출처는 '가정·출처' 시트)</t>
+          <t>작성 [작성일] · [팀명] · 숫자는 매체 견적·합의 자료 기준(출처는 '가정·출처' 시트)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>매체</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>상품·지면</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>시작일</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>종료일</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>예산(원)</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>예상 노출</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>예상 클릭</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>CPM(원)</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>CPC(원)</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>CTR</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>예산 비중</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+          <t>1. 캠페인 개요</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>[매체]</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>[상품·지면]</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
+          <t>브랜드·제품</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>[브랜드·제품]</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
       <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="7">
-        <f>IF(OR(E5="",F5="",F5=0),"",E5/F5*1000)</f>
-        <v/>
-      </c>
-      <c r="I5" s="7">
-        <f>IF(OR(E5="",G5="",G5=0),"",E5/G5)</f>
-        <v/>
-      </c>
-      <c r="J5" s="8">
-        <f>IF(OR(F5="",G5="",F5=0),"",G5/F5)</f>
-        <v/>
-      </c>
-      <c r="K5" s="9">
-        <f>IF(OR(E5="",$E$15=0),"",E5/$E$15)</f>
-        <v/>
-      </c>
-      <c r="L5" s="4" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>캠페인명</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>[캠페인명]</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>배경 및 목적</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>[배경 및 목적 — 이번 미디어 집행으로 이루려는 것]</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
       <c r="G6" s="6" t="n"/>
-      <c r="H6" s="7">
-        <f>IF(OR(E6="",F6="",F6=0),"",E6/F6*1000)</f>
-        <v/>
-      </c>
-      <c r="I6" s="7">
-        <f>IF(OR(E6="",G6="",G6=0),"",E6/G6)</f>
-        <v/>
-      </c>
-      <c r="J6" s="8">
-        <f>IF(OR(F6="",G6="",F6=0),"",G6/F6)</f>
-        <v/>
-      </c>
-      <c r="K6" s="9">
-        <f>IF(OR(E6="",$E$15=0),"",E6/$E$15)</f>
-        <v/>
-      </c>
-      <c r="L6" s="4" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="n"/>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Comm. 타깃</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>[타깃]</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
       <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="7">
-        <f>IF(OR(E7="",F7="",F7=0),"",E7/F7*1000)</f>
-        <v/>
-      </c>
-      <c r="I7" s="7">
-        <f>IF(OR(E7="",G7="",G7=0),"",E7/G7)</f>
-        <v/>
-      </c>
-      <c r="J7" s="8">
-        <f>IF(OR(F7="",G7="",F7=0),"",G7/F7)</f>
-        <v/>
-      </c>
-      <c r="K7" s="9">
-        <f>IF(OR(E7="",$E$15=0),"",E7/$E$15)</f>
-        <v/>
-      </c>
-      <c r="L7" s="4" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n"/>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>캠페인 기간</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>[캠페인 기간]</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>캠페인 목표</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>[캠페인 목표 — 도달·조회·유입·전환 중 무엇, 비중]</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="7">
-        <f>IF(OR(E8="",F8="",F8=0),"",E8/F8*1000)</f>
-        <v/>
-      </c>
-      <c r="I8" s="7">
-        <f>IF(OR(E8="",G8="",G8=0),"",E8/G8)</f>
-        <v/>
-      </c>
-      <c r="J8" s="8">
-        <f>IF(OR(F8="",G8="",F8=0),"",G8/F8)</f>
-        <v/>
-      </c>
-      <c r="K8" s="9">
-        <f>IF(OR(E8="",$E$15=0),"",E8/$E$15)</f>
-        <v/>
-      </c>
-      <c r="L8" s="4" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n"/>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>캠페인 예산</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>[총예산]</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>집행 매체</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>[집행 매체 — 지상파·케이블·디지털·CTV·OOH·기타 중]</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
       <c r="G9" s="6" t="n"/>
-      <c r="H9" s="7">
-        <f>IF(OR(E9="",F9="",F9=0),"",E9/F9*1000)</f>
-        <v/>
-      </c>
-      <c r="I9" s="7">
-        <f>IF(OR(E9="",G9="",G9=0),"",E9/G9)</f>
-        <v/>
-      </c>
-      <c r="J9" s="8">
-        <f>IF(OR(F9="",G9="",F9=0),"",G9/F9)</f>
-        <v/>
-      </c>
-      <c r="K9" s="9">
-        <f>IF(OR(E9="",$E$15=0),"",E9/$E$15)</f>
-        <v/>
-      </c>
-      <c r="L9" s="4" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>운영 소재</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>[운영 소재 — 편 수·초수·형태(가로·세로·이미지)]</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="n"/>
-      <c r="H10" s="7">
-        <f>IF(OR(E10="",F10="",F10=0),"",E10/F10*1000)</f>
-        <v/>
-      </c>
-      <c r="I10" s="7">
-        <f>IF(OR(E10="",G10="",G10=0),"",E10/G10)</f>
-        <v/>
-      </c>
-      <c r="J10" s="8">
-        <f>IF(OR(F10="",G10="",F10=0),"",G10/F10)</f>
-        <v/>
-      </c>
-      <c r="K10" s="9">
-        <f>IF(OR(E10="",$E$15=0),"",E10/$E$15)</f>
-        <v/>
-      </c>
-      <c r="L10" s="4" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="7">
-        <f>IF(OR(E11="",F11="",F11=0),"",E11/F11*1000)</f>
-        <v/>
-      </c>
-      <c r="I11" s="7">
-        <f>IF(OR(E11="",G11="",G11=0),"",E11/G11)</f>
-        <v/>
-      </c>
-      <c r="J11" s="8">
-        <f>IF(OR(F11="",G11="",F11=0),"",G11/F11)</f>
-        <v/>
-      </c>
-      <c r="K11" s="9">
-        <f>IF(OR(E11="",$E$15=0),"",E11/$E$15)</f>
-        <v/>
-      </c>
-      <c r="L11" s="4" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="7">
-        <f>IF(OR(E12="",F12="",F12=0),"",E12/F12*1000)</f>
-        <v/>
-      </c>
-      <c r="I12" s="7">
-        <f>IF(OR(E12="",G12="",G12=0),"",E12/G12)</f>
-        <v/>
-      </c>
-      <c r="J12" s="8">
-        <f>IF(OR(F12="",G12="",F12=0),"",G12/F12)</f>
-        <v/>
-      </c>
-      <c r="K12" s="9">
-        <f>IF(OR(E12="",$E$15=0),"",E12/$E$15)</f>
-        <v/>
-      </c>
-      <c r="L12" s="4" t="n"/>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2. 매체별 집행 계획</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="7">
-        <f>IF(OR(E13="",F13="",F13=0),"",E13/F13*1000)</f>
-        <v/>
-      </c>
-      <c r="I13" s="7">
-        <f>IF(OR(E13="",G13="",G13=0),"",E13/G13)</f>
-        <v/>
-      </c>
-      <c r="J13" s="8">
-        <f>IF(OR(F13="",G13="",F13=0),"",G13/F13)</f>
-        <v/>
-      </c>
-      <c r="K13" s="9">
-        <f>IF(OR(E13="",$E$15=0),"",E13/$E$15)</f>
-        <v/>
-      </c>
-      <c r="L13" s="4" t="n"/>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>매체</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>상품·지면</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>타깃팅</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>시작일</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>종료일</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>예산(원)</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>예상 노출</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>예상 조회</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>예상 클릭</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>CPM(원)</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>CPV(원)</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>예산 비중</t>
+        </is>
+      </c>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="7">
-        <f>IF(OR(E14="",F14="",F14=0),"",E14/F14*1000)</f>
-        <v/>
-      </c>
-      <c r="I14" s="7">
-        <f>IF(OR(E14="",G14="",G14=0),"",E14/G14)</f>
-        <v/>
-      </c>
-      <c r="J14" s="8">
-        <f>IF(OR(F14="",G14="",F14=0),"",G14/F14)</f>
-        <v/>
-      </c>
-      <c r="K14" s="9">
-        <f>IF(OR(E14="",$E$15=0),"",E14/$E$15)</f>
-        <v/>
-      </c>
-      <c r="L14" s="4" t="n"/>
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="10" t="n"/>
+      <c r="J14" s="10" t="n"/>
+      <c r="K14" s="11">
+        <f>IF(OR(G14="",H14="",H14=0),"",G14/H14*1000)</f>
+        <v/>
+      </c>
+      <c r="L14" s="11">
+        <f>IF(OR(G14="",I14="",I14=0),"",G14/I14)</f>
+        <v/>
+      </c>
+      <c r="M14" s="12">
+        <f>IF(OR(H14="",J14="",H14=0),"",J14/H14)</f>
+        <v/>
+      </c>
+      <c r="N14" s="13">
+        <f>IF(OR(G14="",$G$26=0),"",G14/$G$26)</f>
+        <v/>
+      </c>
+      <c r="O14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="10" t="n"/>
+      <c r="H15" s="10" t="n"/>
+      <c r="I15" s="10" t="n"/>
+      <c r="J15" s="10" t="n"/>
+      <c r="K15" s="11">
+        <f>IF(OR(G15="",H15="",H15=0),"",G15/H15*1000)</f>
+        <v/>
+      </c>
+      <c r="L15" s="11">
+        <f>IF(OR(G15="",I15="",I15=0),"",G15/I15)</f>
+        <v/>
+      </c>
+      <c r="M15" s="12">
+        <f>IF(OR(H15="",J15="",H15=0),"",J15/H15)</f>
+        <v/>
+      </c>
+      <c r="N15" s="13">
+        <f>IF(OR(G15="",$G$26=0),"",G15/$G$26)</f>
+        <v/>
+      </c>
+      <c r="O15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="10" t="n"/>
+      <c r="H16" s="10" t="n"/>
+      <c r="I16" s="10" t="n"/>
+      <c r="J16" s="10" t="n"/>
+      <c r="K16" s="11">
+        <f>IF(OR(G16="",H16="",H16=0),"",G16/H16*1000)</f>
+        <v/>
+      </c>
+      <c r="L16" s="11">
+        <f>IF(OR(G16="",I16="",I16=0),"",G16/I16)</f>
+        <v/>
+      </c>
+      <c r="M16" s="12">
+        <f>IF(OR(H16="",J16="",H16=0),"",J16/H16)</f>
+        <v/>
+      </c>
+      <c r="N16" s="13">
+        <f>IF(OR(G16="",$G$26=0),"",G16/$G$26)</f>
+        <v/>
+      </c>
+      <c r="O16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="10" t="n"/>
+      <c r="I17" s="10" t="n"/>
+      <c r="J17" s="10" t="n"/>
+      <c r="K17" s="11">
+        <f>IF(OR(G17="",H17="",H17=0),"",G17/H17*1000)</f>
+        <v/>
+      </c>
+      <c r="L17" s="11">
+        <f>IF(OR(G17="",I17="",I17=0),"",G17/I17)</f>
+        <v/>
+      </c>
+      <c r="M17" s="12">
+        <f>IF(OR(H17="",J17="",H17=0),"",J17/H17)</f>
+        <v/>
+      </c>
+      <c r="N17" s="13">
+        <f>IF(OR(G17="",$G$26=0),"",G17/$G$26)</f>
+        <v/>
+      </c>
+      <c r="O17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="10" t="n"/>
+      <c r="I18" s="10" t="n"/>
+      <c r="J18" s="10" t="n"/>
+      <c r="K18" s="11">
+        <f>IF(OR(G18="",H18="",H18=0),"",G18/H18*1000)</f>
+        <v/>
+      </c>
+      <c r="L18" s="11">
+        <f>IF(OR(G18="",I18="",I18=0),"",G18/I18)</f>
+        <v/>
+      </c>
+      <c r="M18" s="12">
+        <f>IF(OR(H18="",J18="",H18=0),"",J18/H18)</f>
+        <v/>
+      </c>
+      <c r="N18" s="13">
+        <f>IF(OR(G18="",$G$26=0),"",G18/$G$26)</f>
+        <v/>
+      </c>
+      <c r="O18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="10" t="n"/>
+      <c r="I19" s="10" t="n"/>
+      <c r="J19" s="10" t="n"/>
+      <c r="K19" s="11">
+        <f>IF(OR(G19="",H19="",H19=0),"",G19/H19*1000)</f>
+        <v/>
+      </c>
+      <c r="L19" s="11">
+        <f>IF(OR(G19="",I19="",I19=0),"",G19/I19)</f>
+        <v/>
+      </c>
+      <c r="M19" s="12">
+        <f>IF(OR(H19="",J19="",H19=0),"",J19/H19)</f>
+        <v/>
+      </c>
+      <c r="N19" s="13">
+        <f>IF(OR(G19="",$G$26=0),"",G19/$G$26)</f>
+        <v/>
+      </c>
+      <c r="O19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="10" t="n"/>
+      <c r="H20" s="10" t="n"/>
+      <c r="I20" s="10" t="n"/>
+      <c r="J20" s="10" t="n"/>
+      <c r="K20" s="11">
+        <f>IF(OR(G20="",H20="",H20=0),"",G20/H20*1000)</f>
+        <v/>
+      </c>
+      <c r="L20" s="11">
+        <f>IF(OR(G20="",I20="",I20=0),"",G20/I20)</f>
+        <v/>
+      </c>
+      <c r="M20" s="12">
+        <f>IF(OR(H20="",J20="",H20=0),"",J20/H20)</f>
+        <v/>
+      </c>
+      <c r="N20" s="13">
+        <f>IF(OR(G20="",$G$26=0),"",G20/$G$26)</f>
+        <v/>
+      </c>
+      <c r="O20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n"/>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="10" t="n"/>
+      <c r="I21" s="10" t="n"/>
+      <c r="J21" s="10" t="n"/>
+      <c r="K21" s="11">
+        <f>IF(OR(G21="",H21="",H21=0),"",G21/H21*1000)</f>
+        <v/>
+      </c>
+      <c r="L21" s="11">
+        <f>IF(OR(G21="",I21="",I21=0),"",G21/I21)</f>
+        <v/>
+      </c>
+      <c r="M21" s="12">
+        <f>IF(OR(H21="",J21="",H21=0),"",J21/H21)</f>
+        <v/>
+      </c>
+      <c r="N21" s="13">
+        <f>IF(OR(G21="",$G$26=0),"",G21/$G$26)</f>
+        <v/>
+      </c>
+      <c r="O21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="10" t="n"/>
+      <c r="H22" s="10" t="n"/>
+      <c r="I22" s="10" t="n"/>
+      <c r="J22" s="10" t="n"/>
+      <c r="K22" s="11">
+        <f>IF(OR(G22="",H22="",H22=0),"",G22/H22*1000)</f>
+        <v/>
+      </c>
+      <c r="L22" s="11">
+        <f>IF(OR(G22="",I22="",I22=0),"",G22/I22)</f>
+        <v/>
+      </c>
+      <c r="M22" s="12">
+        <f>IF(OR(H22="",J22="",H22=0),"",J22/H22)</f>
+        <v/>
+      </c>
+      <c r="N22" s="13">
+        <f>IF(OR(G22="",$G$26=0),"",G22/$G$26)</f>
+        <v/>
+      </c>
+      <c r="O22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="10" t="n"/>
+      <c r="H23" s="10" t="n"/>
+      <c r="I23" s="10" t="n"/>
+      <c r="J23" s="10" t="n"/>
+      <c r="K23" s="11">
+        <f>IF(OR(G23="",H23="",H23=0),"",G23/H23*1000)</f>
+        <v/>
+      </c>
+      <c r="L23" s="11">
+        <f>IF(OR(G23="",I23="",I23=0),"",G23/I23)</f>
+        <v/>
+      </c>
+      <c r="M23" s="12">
+        <f>IF(OR(H23="",J23="",H23=0),"",J23/H23)</f>
+        <v/>
+      </c>
+      <c r="N23" s="13">
+        <f>IF(OR(G23="",$G$26=0),"",G23/$G$26)</f>
+        <v/>
+      </c>
+      <c r="O23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="10" t="n"/>
+      <c r="I24" s="10" t="n"/>
+      <c r="J24" s="10" t="n"/>
+      <c r="K24" s="11">
+        <f>IF(OR(G24="",H24="",H24=0),"",G24/H24*1000)</f>
+        <v/>
+      </c>
+      <c r="L24" s="11">
+        <f>IF(OR(G24="",I24="",I24=0),"",G24/I24)</f>
+        <v/>
+      </c>
+      <c r="M24" s="12">
+        <f>IF(OR(H24="",J24="",H24=0),"",J24/H24)</f>
+        <v/>
+      </c>
+      <c r="N24" s="13">
+        <f>IF(OR(G24="",$G$26=0),"",G24/$G$26)</f>
+        <v/>
+      </c>
+      <c r="O24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="n"/>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="10" t="n"/>
+      <c r="I25" s="10" t="n"/>
+      <c r="J25" s="10" t="n"/>
+      <c r="K25" s="11">
+        <f>IF(OR(G25="",H25="",H25=0),"",G25/H25*1000)</f>
+        <v/>
+      </c>
+      <c r="L25" s="11">
+        <f>IF(OR(G25="",I25="",I25=0),"",G25/I25)</f>
+        <v/>
+      </c>
+      <c r="M25" s="12">
+        <f>IF(OR(H25="",J25="",H25=0),"",J25/H25)</f>
+        <v/>
+      </c>
+      <c r="N25" s="13">
+        <f>IF(OR(G25="",$G$26=0),"",G25/$G$26)</f>
+        <v/>
+      </c>
+      <c r="O25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="11">
-        <f>SUM(E5:E14)</f>
-        <v/>
-      </c>
-      <c r="F15" s="11">
-        <f>SUM(F5:F14)</f>
-        <v/>
-      </c>
-      <c r="G15" s="11">
-        <f>SUM(G5:G14)</f>
-        <v/>
-      </c>
-      <c r="H15" s="11">
-        <f>IF(F15=0,"",E15/F15*1000)</f>
-        <v/>
-      </c>
-      <c r="I15" s="11">
-        <f>IF(G15=0,"",E15/G15)</f>
-        <v/>
-      </c>
-      <c r="J15" s="12">
-        <f>IF(F15=0,"",G15/F15)</f>
-        <v/>
-      </c>
-      <c r="K15" s="13">
-        <f>IF(E15=0,"",1)</f>
-        <v/>
-      </c>
-      <c r="L15" s="10" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>회색 칸은 계산식. 예산·노출·클릭만 넣는다.</t>
-        </is>
-      </c>
+      <c r="B26" s="14" t="n"/>
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="14" t="n"/>
+      <c r="E26" s="14" t="n"/>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="15">
+        <f>SUM(G14:G25)</f>
+        <v/>
+      </c>
+      <c r="H26" s="15">
+        <f>SUM(H14:H25)</f>
+        <v/>
+      </c>
+      <c r="I26" s="15">
+        <f>SUM(I14:I25)</f>
+        <v/>
+      </c>
+      <c r="J26" s="15">
+        <f>SUM(J14:J25)</f>
+        <v/>
+      </c>
+      <c r="K26" s="15">
+        <f>IF(H26=0,"",G26/H26*1000)</f>
+        <v/>
+      </c>
+      <c r="L26" s="15">
+        <f>IF(I26=0,"",G26/I26)</f>
+        <v/>
+      </c>
+      <c r="M26" s="16">
+        <f>IF(H26=0,"",J26/H26)</f>
+        <v/>
+      </c>
+      <c r="N26" s="17">
+        <f>IF(G26=0,"",1)</f>
+        <v/>
+      </c>
+      <c r="O26" s="14" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>구분은 지상파·케이블·디지털·CTV·OOH·기타 중 하나로. 회색 칸은 계산식, 예산·노출·조회·클릭만 넣는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>3. 매체 구분별 예산 요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>매체 구분</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>예산(원)</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>비중</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>지상파</t>
+        </is>
+      </c>
+      <c r="B31" s="11">
+        <f>SUMIF($A$14:$A$25,A31,$G$14:$G$25)</f>
+        <v/>
+      </c>
+      <c r="C31" s="13">
+        <f>IF($G$26=0,"",B31/$G$26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>케이블</t>
+        </is>
+      </c>
+      <c r="B32" s="11">
+        <f>SUMIF($A$14:$A$25,A32,$G$14:$G$25)</f>
+        <v/>
+      </c>
+      <c r="C32" s="13">
+        <f>IF($G$26=0,"",B32/$G$26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>디지털</t>
+        </is>
+      </c>
+      <c r="B33" s="11">
+        <f>SUMIF($A$14:$A$25,A33,$G$14:$G$25)</f>
+        <v/>
+      </c>
+      <c r="C33" s="13">
+        <f>IF($G$26=0,"",B33/$G$26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>CTV</t>
+        </is>
+      </c>
+      <c r="B34" s="11">
+        <f>SUMIF($A$14:$A$25,A34,$G$14:$G$25)</f>
+        <v/>
+      </c>
+      <c r="C34" s="13">
+        <f>IF($G$26=0,"",B34/$G$26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>OOH</t>
+        </is>
+      </c>
+      <c r="B35" s="11">
+        <f>SUMIF($A$14:$A$25,A35,$G$14:$G$25)</f>
+        <v/>
+      </c>
+      <c r="C35" s="13">
+        <f>IF($G$26=0,"",B35/$G$26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="B36" s="11">
+        <f>SUMIF($A$14:$A$25,A36,$G$14:$G$25)</f>
+        <v/>
+      </c>
+      <c r="C36" s="13">
+        <f>IF($G$26=0,"",B36/$G$26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B37" s="15">
+        <f>SUM(B31:B36)</f>
+        <v/>
+      </c>
+      <c r="C37" s="14">
+        <f>IF(B37=$G$26,"집행 계획 합계와 같음","구분을 확인하세요")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>4. 소재 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>소재</t>
+        </is>
+      </c>
+      <c r="B41" s="18" t="inlineStr">
+        <is>
+          <t>유형</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>초수·규격</t>
+        </is>
+      </c>
+      <c r="D41" s="18" t="inlineStr">
+        <is>
+          <t>운영 비중</t>
+        </is>
+      </c>
+      <c r="E41" s="18" t="inlineStr">
+        <is>
+          <t>소재 특성·키 메시지</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="n"/>
+      <c r="B42" s="8" t="n"/>
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="8" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="n"/>
+      <c r="B43" s="8" t="n"/>
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="8" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="n"/>
+      <c r="B44" s="8" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="n"/>
+      <c r="B45" s="8" t="n"/>
+      <c r="C45" s="8" t="n"/>
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="8" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="n"/>
+      <c r="B46" s="8" t="n"/>
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="8" t="n"/>
+      <c r="E46" s="8" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="n"/>
+      <c r="B47" s="8" t="n"/>
+      <c r="C47" s="8" t="n"/>
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="8" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>5. 매체별 운영 메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[TV 운영 메모 — 지상파·케이블 비중, 선호 채널·프로그램]</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="n"/>
+      <c r="F50" s="6" t="n"/>
+      <c r="G50" s="6" t="n"/>
+      <c r="H50" s="6" t="n"/>
+      <c r="I50" s="6" t="n"/>
+      <c r="J50" s="6" t="n"/>
+      <c r="K50" s="6" t="n"/>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>디지털</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[디지털 운영 메모 — 필수 매체, 타깃팅 기준]</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="6" t="n"/>
+      <c r="F51" s="6" t="n"/>
+      <c r="G51" s="6" t="n"/>
+      <c r="H51" s="6" t="n"/>
+      <c r="I51" s="6" t="n"/>
+      <c r="J51" s="6" t="n"/>
+      <c r="K51" s="6" t="n"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>CTV·OOH</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>[CTV·OOH 운영 메모 — 선호 매체·지역]</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="6" t="n"/>
+      <c r="F52" s="6" t="n"/>
+      <c r="G52" s="6" t="n"/>
+      <c r="H52" s="6" t="n"/>
+      <c r="I52" s="6" t="n"/>
+      <c r="J52" s="6" t="n"/>
+      <c r="K52" s="6" t="n"/>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>특이 사항</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[운영 특이 사항 — 제외 매체·광고주 요청]</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n"/>
+      <c r="F53" s="6" t="n"/>
+      <c r="G53" s="6" t="n"/>
+      <c r="H53" s="6" t="n"/>
+      <c r="I53" s="6" t="n"/>
+      <c r="J53" s="6" t="n"/>
+      <c r="K53" s="6" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="H7:L7"/>
+    <mergeCell ref="B50:K50"/>
+    <mergeCell ref="B9:K9"/>
+    <mergeCell ref="B52:K52"/>
+    <mergeCell ref="B53:K53"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B6:K6"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="B10:K10"/>
+    <mergeCell ref="H8:L8"/>
+    <mergeCell ref="B51:K51"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -914,7 +1558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -923,62 +1567,68 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>가정·출처</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>값·가정</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>출처(자료명·날짜)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>[예: 매체 견적]</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
+      <c r="A4" s="8" t="n"/>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n"/>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n"/>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n"/>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
